--- a/Aug_2026/daily Reports/STT Report Elite Marketing JULY_26.xlsx
+++ b/Aug_2026/daily Reports/STT Report Elite Marketing JULY_26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8334AC0F-275E-485A-80CE-BE09CB81D367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9425ED4-7981-435C-A139-7EA2A3C7DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -3211,10 +3211,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3223,16 +3226,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3619,47 +3619,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="123" t="s">
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="123" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="F1" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="123" t="s">
+      <c r="H1" s="119" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J1" s="42"/>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="125" t="s">
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="121" t="s">
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122" t="s">
         <v>10</v>
       </c>
       <c r="T1" s="124" t="s">
@@ -3674,61 +3674,61 @@
       <c r="Y1" s="124"/>
       <c r="Z1" s="124"/>
       <c r="AA1" s="124"/>
-      <c r="AB1" s="121" t="s">
+      <c r="AB1" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="121" t="s">
+      <c r="AC1" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="121" t="s">
+      <c r="AD1" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="121" t="s">
+      <c r="AE1" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="121" t="s">
+      <c r="AF1" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="121" t="s">
+      <c r="AG1" s="122" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="84">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="121" t="s">
+      <c r="AI1" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="121" t="s">
+      <c r="AJ1" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="121" t="s">
+      <c r="AK1" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="121" t="s">
+      <c r="AL1" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="121" t="s">
+      <c r="AM1" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="119" t="s">
+      <c r="AN1" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="119" t="s">
+      <c r="AO1" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="121" t="s">
+      <c r="AP1" s="122" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="123"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
+      <c r="A2" s="119"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
@@ -3759,7 +3759,7 @@
       <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="122"/>
+      <c r="S2" s="123"/>
       <c r="T2" s="83" t="s">
         <v>73</v>
       </c>
@@ -3784,25 +3784,25 @@
       <c r="AA2" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="123"/>
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="123"/>
+      <c r="AG2" s="123"/>
       <c r="AH2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="122"/>
-      <c r="AJ2" s="122"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="122"/>
-      <c r="AM2" s="122"/>
-      <c r="AN2" s="120"/>
-      <c r="AO2" s="120"/>
-      <c r="AP2" s="122"/>
-    </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="123"/>
+      <c r="AL2" s="123"/>
+      <c r="AM2" s="123"/>
+      <c r="AN2" s="126"/>
+      <c r="AO2" s="126"/>
+      <c r="AP2" s="123"/>
+    </row>
+    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="85">
         <v>46204</v>
       </c>
@@ -3913,7 +3913,7 @@
       <c r="AO3" s="3"/>
       <c r="AP3" s="92"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="85">
         <v>46204</v>
       </c>
@@ -4025,7 +4025,7 @@
       <c r="AO4" s="3"/>
       <c r="AP4" s="92"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="85">
         <v>46204</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="AO5" s="3"/>
       <c r="AP5" s="92"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="85">
         <v>46204</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="92"/>
     </row>
-    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:42" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="85">
         <v>46204</v>
       </c>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AP7" s="92"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="85">
         <v>46204</v>
       </c>
@@ -4468,7 +4468,7 @@
       <c r="AN8"/>
       <c r="AP8" s="92"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="85">
         <v>46204</v>
       </c>
@@ -4575,7 +4575,7 @@
       <c r="AN9"/>
       <c r="AP9" s="92"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="85">
         <v>46204</v>
       </c>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="AP10" s="92"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="85">
         <v>46204</v>
       </c>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AP11" s="92"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="85">
         <v>46204</v>
       </c>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AP12" s="92"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="85">
         <v>46204</v>
       </c>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AP13" s="92"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="85">
         <v>46204</v>
       </c>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AP14" s="92"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="85">
         <v>46204</v>
       </c>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="AP33" s="92"/>
     </row>
-    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" s="85">
         <v>46204</v>
       </c>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AP34" s="92"/>
     </row>
-    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" s="85">
         <v>46204</v>
       </c>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="AP35" s="92"/>
     </row>
-    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" s="85">
         <v>46204</v>
       </c>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AP36" s="92"/>
     </row>
-    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" s="85">
         <v>46204</v>
       </c>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AP37" s="92"/>
     </row>
-    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" s="85">
         <v>46204</v>
       </c>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="AP38" s="92"/>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="85">
         <v>46205</v>
       </c>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="AP65" s="92"/>
     </row>
-    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" s="85">
         <v>46205</v>
       </c>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="AP66" s="92"/>
     </row>
-    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" s="85">
         <v>46205</v>
       </c>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AP67" s="92"/>
     </row>
-    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" s="85">
         <v>46205</v>
       </c>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AP68" s="92"/>
     </row>
-    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" s="85">
         <v>46205</v>
       </c>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="AP69" s="92"/>
     </row>
-    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" s="85">
         <v>46205</v>
       </c>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AP70" s="92"/>
     </row>
-    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" s="85">
         <v>46205</v>
       </c>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="AP71" s="92"/>
     </row>
-    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" s="85">
         <v>46205</v>
       </c>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="AP72" s="92"/>
     </row>
-    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" s="85">
         <v>46205</v>
       </c>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="AP73" s="92"/>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="85">
         <v>46205</v>
       </c>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AP74" s="92"/>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="85">
         <v>46205</v>
       </c>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AP75" s="92"/>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="85">
         <v>46205</v>
       </c>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="AP76" s="92"/>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="85">
         <v>46205</v>
       </c>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="AP77" s="92"/>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="85">
         <v>46206</v>
       </c>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="AP78" s="92"/>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="85">
         <v>46206</v>
       </c>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AP79" s="92"/>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="85">
         <v>46206</v>
       </c>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AP98" s="92"/>
     </row>
-    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A99" s="85">
         <v>46206</v>
       </c>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="AP99" s="92"/>
     </row>
-    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A100" s="85">
         <v>46206</v>
       </c>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="AP100" s="92"/>
     </row>
-    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A101" s="85">
         <v>46206</v>
       </c>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="AP101" s="92"/>
     </row>
-    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A102" s="85">
         <v>46206</v>
       </c>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="AP102" s="92"/>
     </row>
-    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A103" s="85">
         <v>46206</v>
       </c>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="AP103" s="92"/>
     </row>
-    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A104" s="85">
         <v>46206</v>
       </c>
@@ -14260,7 +14260,7 @@
       </c>
       <c r="AP104" s="92"/>
     </row>
-    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A105" s="85">
         <v>46206</v>
       </c>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="AP105" s="92"/>
     </row>
-    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A106" s="85">
         <v>46206</v>
       </c>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="AP106" s="92"/>
     </row>
-    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A107" s="85">
         <v>46206</v>
       </c>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="AP126" s="92"/>
     </row>
-    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" s="85">
         <v>46207</v>
       </c>
@@ -16580,7 +16580,7 @@
       </c>
       <c r="AP127" s="92"/>
     </row>
-    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" s="85">
         <v>46207</v>
       </c>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="AP128" s="92"/>
     </row>
-    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" s="85">
         <v>46207</v>
       </c>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="AP129" s="92"/>
     </row>
-    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" s="85">
         <v>46207</v>
       </c>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="AP130" s="92"/>
     </row>
-    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" s="85">
         <v>46207</v>
       </c>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="AP131" s="92"/>
     </row>
-    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" s="85">
         <v>46207</v>
       </c>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="AP132" s="92"/>
     </row>
-    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" s="85">
         <v>46207</v>
       </c>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="AP133" s="92"/>
     </row>
-    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" s="85">
         <v>46207</v>
       </c>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="AP134" s="92"/>
     </row>
-    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" s="85">
         <v>46207</v>
       </c>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="AP135" s="92"/>
     </row>
-    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" s="85">
         <v>46207</v>
       </c>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="AP136" s="92"/>
     </row>
-    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" s="85">
         <v>46207</v>
       </c>
@@ -19620,7 +19620,7 @@
       </c>
       <c r="AP157" s="92"/>
     </row>
-    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A158" s="85">
         <v>46209</v>
       </c>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="AP158" s="92"/>
     </row>
-    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A159" s="85">
         <v>46209</v>
       </c>
@@ -19816,7 +19816,7 @@
       </c>
       <c r="AP159" s="92"/>
     </row>
-    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A160" s="85">
         <v>46209</v>
       </c>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AP160" s="92"/>
     </row>
-    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A161" s="85">
         <v>46209</v>
       </c>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="AP161" s="92"/>
     </row>
-    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A162" s="85">
         <v>46209</v>
       </c>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="AP162" s="92"/>
     </row>
-    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A163" s="85">
         <v>46209</v>
       </c>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="AP163" s="92"/>
     </row>
-    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A164" s="85">
         <v>46209</v>
       </c>
@@ -20312,7 +20312,7 @@
       </c>
       <c r="AP164" s="92"/>
     </row>
-    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A165" s="85">
         <v>46209</v>
       </c>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="AP165" s="92"/>
     </row>
-    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A166" s="85">
         <v>46209</v>
       </c>
@@ -20508,7 +20508,7 @@
       </c>
       <c r="AP166" s="92"/>
     </row>
-    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A167" s="85">
         <v>46209</v>
       </c>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="AP170" s="92"/>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="85">
         <v>46210</v>
       </c>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="AP171" s="92"/>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="85">
         <v>46210</v>
       </c>
@@ -23132,7 +23132,7 @@
       </c>
       <c r="AP192" s="92"/>
     </row>
-    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A193" s="85">
         <v>46210</v>
       </c>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="AP193" s="92"/>
     </row>
-    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A194" s="85">
         <v>46210</v>
       </c>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="AP194" s="92"/>
     </row>
-    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A195" s="85">
         <v>46210</v>
       </c>
@@ -23426,7 +23426,7 @@
       </c>
       <c r="AP195" s="92"/>
     </row>
-    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A196" s="85">
         <v>46210</v>
       </c>
@@ -23524,7 +23524,7 @@
       </c>
       <c r="AP196" s="92"/>
     </row>
-    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A197" s="85">
         <v>46210</v>
       </c>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="AP197" s="92"/>
     </row>
-    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A198" s="85">
         <v>46210</v>
       </c>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="AP198" s="92"/>
     </row>
-    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A199" s="85">
         <v>46210</v>
       </c>
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AP199" s="92"/>
     </row>
-    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A200" s="85">
         <v>46210</v>
       </c>
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AP200" s="92"/>
     </row>
-    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A201" s="85">
         <v>46210</v>
       </c>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="AP218" s="92"/>
     </row>
-    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A219" s="85">
         <v>46211</v>
       </c>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="AP219" s="92"/>
     </row>
-    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A220" s="85">
         <v>46211</v>
       </c>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="AP220" s="92"/>
     </row>
-    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A221" s="85">
         <v>46211</v>
       </c>
@@ -26024,7 +26024,7 @@
       </c>
       <c r="AP221" s="92"/>
     </row>
-    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A222" s="85">
         <v>46211</v>
       </c>
@@ -26122,7 +26122,7 @@
       </c>
       <c r="AP222" s="92"/>
     </row>
-    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A223" s="85">
         <v>46211</v>
       </c>
@@ -26220,7 +26220,7 @@
       </c>
       <c r="AP223" s="92"/>
     </row>
-    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A224" s="85">
         <v>46211</v>
       </c>
@@ -26318,7 +26318,7 @@
       </c>
       <c r="AP224" s="92"/>
     </row>
-    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A225" s="85">
         <v>46211</v>
       </c>
@@ -26416,7 +26416,7 @@
       </c>
       <c r="AP225" s="92"/>
     </row>
-    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A226" s="85">
         <v>46211</v>
       </c>
@@ -26514,7 +26514,7 @@
       </c>
       <c r="AP226" s="92"/>
     </row>
-    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A227" s="85">
         <v>46211</v>
       </c>
@@ -26618,7 +26618,7 @@
       </c>
       <c r="AP227" s="92"/>
     </row>
-    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A228" s="85">
         <v>46211</v>
       </c>
@@ -26718,7 +26718,7 @@
       </c>
       <c r="AP228" s="92"/>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="85">
         <v>46212</v>
       </c>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="AP229" s="92"/>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="85">
         <v>46212</v>
       </c>
@@ -26924,7 +26924,7 @@
       </c>
       <c r="AP230" s="92"/>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="85">
         <v>46212</v>
       </c>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="AP247" s="92"/>
     </row>
-    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A248" s="85">
         <v>46212</v>
       </c>
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AP248" s="92"/>
     </row>
-    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A249" s="85">
         <v>46212</v>
       </c>
@@ -28850,7 +28850,7 @@
       </c>
       <c r="AP249" s="92"/>
     </row>
-    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A250" s="85">
         <v>46212</v>
       </c>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="AP250" s="92"/>
     </row>
-    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A251" s="85">
         <v>46212</v>
       </c>
@@ -29050,7 +29050,7 @@
       </c>
       <c r="AP251" s="92"/>
     </row>
-    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A252" s="85">
         <v>46212</v>
       </c>
@@ -29152,7 +29152,7 @@
       </c>
       <c r="AP252" s="92"/>
     </row>
-    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A253" s="85">
         <v>46212</v>
       </c>
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AP253" s="92"/>
     </row>
-    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A254" s="85">
         <v>46212</v>
       </c>
@@ -29358,7 +29358,7 @@
       </c>
       <c r="AP254" s="92"/>
     </row>
-    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A255" s="85">
         <v>46212</v>
       </c>
@@ -29458,7 +29458,7 @@
       </c>
       <c r="AP255" s="92"/>
     </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="85">
         <v>46213</v>
       </c>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="AP256" s="92"/>
     </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="85">
         <v>46213</v>
       </c>
@@ -29670,7 +29670,7 @@
       </c>
       <c r="AP257" s="92"/>
     </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="85">
         <v>46213</v>
       </c>
@@ -29772,7 +29772,7 @@
       </c>
       <c r="AP258" s="92"/>
     </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="85">
         <v>46213</v>
       </c>
@@ -29880,7 +29880,7 @@
       </c>
       <c r="AP259" s="92"/>
     </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="85">
         <v>46213</v>
       </c>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="AP260" s="92"/>
     </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="85">
         <v>46213</v>
       </c>
@@ -31594,7 +31594,7 @@
       </c>
       <c r="AP276" s="92"/>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="85">
         <v>46213</v>
       </c>
@@ -31692,7 +31692,7 @@
       </c>
       <c r="AP277" s="92"/>
     </row>
-    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A278" s="85">
         <v>46213</v>
       </c>
@@ -33942,7 +33942,7 @@
       </c>
       <c r="AP299" s="92"/>
     </row>
-    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A300" s="85">
         <v>46214</v>
       </c>
@@ -34050,7 +34050,7 @@
       </c>
       <c r="AP300" s="92"/>
     </row>
-    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A301" s="85">
         <v>46214</v>
       </c>
@@ -34152,7 +34152,7 @@
       </c>
       <c r="AP301" s="92"/>
     </row>
-    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A302" s="85">
         <v>46214</v>
       </c>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="AP302" s="92"/>
     </row>
-    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A303" s="85">
         <v>46214</v>
       </c>
@@ -34350,7 +34350,7 @@
       </c>
       <c r="AP303" s="92"/>
     </row>
-    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A304" s="85">
         <v>46214</v>
       </c>
@@ -34448,7 +34448,7 @@
       </c>
       <c r="AP304" s="92"/>
     </row>
-    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A305" s="85">
         <v>46214</v>
       </c>
@@ -34546,7 +34546,7 @@
       </c>
       <c r="AP305" s="92"/>
     </row>
-    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A306" s="85">
         <v>46214</v>
       </c>
@@ -34644,7 +34644,7 @@
       </c>
       <c r="AP306" s="92"/>
     </row>
-    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A307" s="85">
         <v>46214</v>
       </c>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="AP307" s="92"/>
     </row>
-    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A308" s="85">
         <v>46214</v>
       </c>
@@ -34840,7 +34840,7 @@
       </c>
       <c r="AP308" s="92"/>
     </row>
-    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A309" s="85">
         <v>46214</v>
       </c>
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AP309" s="92"/>
     </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="85">
         <v>46214</v>
       </c>
@@ -35044,7 +35044,7 @@
       </c>
       <c r="AP310" s="92"/>
     </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="85">
         <v>46214</v>
       </c>
@@ -35146,7 +35146,7 @@
       </c>
       <c r="AP311" s="92"/>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="85">
         <v>46214</v>
       </c>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="AP312" s="92"/>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="85">
         <v>46214</v>
       </c>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="AP313" s="92"/>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="85">
         <v>46214</v>
       </c>
@@ -44734,7 +44734,7 @@
       </c>
       <c r="AP433" s="92"/>
     </row>
-    <row r="434" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="85">
         <v>46207</v>
       </c>
@@ -45674,7 +45674,7 @@
       </c>
       <c r="AP443" s="7"/>
     </row>
-    <row r="444" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A444" s="85">
         <v>46216</v>
       </c>
@@ -45764,7 +45764,7 @@
       </c>
       <c r="AP444" s="7"/>
     </row>
-    <row r="445" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A445" s="85">
         <v>46216</v>
       </c>
@@ -45854,7 +45854,7 @@
       </c>
       <c r="AP445" s="7"/>
     </row>
-    <row r="446" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A446" s="85">
         <v>46216</v>
       </c>
@@ -45952,7 +45952,7 @@
       </c>
       <c r="AP446" s="7"/>
     </row>
-    <row r="447" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A447" s="85">
         <v>46216</v>
       </c>
@@ -46042,7 +46042,7 @@
       </c>
       <c r="AP447" s="7"/>
     </row>
-    <row r="448" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A448" s="85">
         <v>46216</v>
       </c>
@@ -46142,7 +46142,7 @@
       </c>
       <c r="AP448" s="7"/>
     </row>
-    <row r="449" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A449" s="85">
         <v>46216</v>
       </c>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="AP449" s="7"/>
     </row>
-    <row r="450" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A450" s="85">
         <v>46216</v>
       </c>
@@ -46332,7 +46332,7 @@
       </c>
       <c r="AP450" s="7"/>
     </row>
-    <row r="451" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A451" s="85">
         <v>46216</v>
       </c>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="AP451" s="7"/>
     </row>
-    <row r="452" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="85">
         <v>46216</v>
       </c>
@@ -46526,7 +46526,7 @@
       </c>
       <c r="AP452" s="7"/>
     </row>
-    <row r="453" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="85">
         <v>46216</v>
       </c>
@@ -46616,7 +46616,7 @@
       </c>
       <c r="AP453" s="7"/>
     </row>
-    <row r="454" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="85">
         <v>46216</v>
       </c>
@@ -46716,7 +46716,7 @@
       </c>
       <c r="AP454" s="7"/>
     </row>
-    <row r="455" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="85">
         <v>46216</v>
       </c>
@@ -46812,7 +46812,7 @@
       </c>
       <c r="AP455" s="7"/>
     </row>
-    <row r="456" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="85">
         <v>46216</v>
       </c>
@@ -46906,7 +46906,7 @@
       </c>
       <c r="AP456" s="7"/>
     </row>
-    <row r="457" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="85">
         <v>46216</v>
       </c>
@@ -47000,7 +47000,7 @@
       </c>
       <c r="AP457" s="7"/>
     </row>
-    <row r="458" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="85">
         <v>46217</v>
       </c>
@@ -49848,7 +49848,7 @@
       </c>
       <c r="AP488" s="7"/>
     </row>
-    <row r="489" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A489" s="85">
         <v>46217</v>
       </c>
@@ -49938,7 +49938,7 @@
       </c>
       <c r="AP489" s="7"/>
     </row>
-    <row r="490" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A490" s="85">
         <v>46217</v>
       </c>
@@ -50028,7 +50028,7 @@
       </c>
       <c r="AP490" s="7"/>
     </row>
-    <row r="491" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A491" s="85">
         <v>46217</v>
       </c>
@@ -50118,7 +50118,7 @@
       </c>
       <c r="AP491" s="7"/>
     </row>
-    <row r="492" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A492" s="85">
         <v>46217</v>
       </c>
@@ -50208,7 +50208,7 @@
       </c>
       <c r="AP492" s="7"/>
     </row>
-    <row r="493" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A493" s="85">
         <v>46217</v>
       </c>
@@ -50298,7 +50298,7 @@
       </c>
       <c r="AP493" s="7"/>
     </row>
-    <row r="494" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A494" s="85">
         <v>46217</v>
       </c>
@@ -50392,7 +50392,7 @@
       </c>
       <c r="AP494" s="7"/>
     </row>
-    <row r="495" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A495" s="85">
         <v>46217</v>
       </c>
@@ -50490,7 +50490,7 @@
       </c>
       <c r="AP495" s="7"/>
     </row>
-    <row r="496" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A496" s="85">
         <v>46217</v>
       </c>
@@ -50590,7 +50590,7 @@
       </c>
       <c r="AP496" s="7"/>
     </row>
-    <row r="497" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A497" s="85">
         <v>46217</v>
       </c>
@@ -50680,7 +50680,7 @@
       </c>
       <c r="AP497" s="7"/>
     </row>
-    <row r="498" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A498" s="85">
         <v>46217</v>
       </c>
@@ -50770,7 +50770,7 @@
       </c>
       <c r="AP498" s="7"/>
     </row>
-    <row r="499" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A499" s="85">
         <v>46217</v>
       </c>
@@ -50860,7 +50860,7 @@
       </c>
       <c r="AP499" s="7"/>
     </row>
-    <row r="500" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A500" s="85">
         <v>46217</v>
       </c>
@@ -50950,7 +50950,7 @@
       </c>
       <c r="AP500" s="7"/>
     </row>
-    <row r="501" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A501" s="85">
         <v>46217</v>
       </c>
@@ -52918,7 +52918,7 @@
       </c>
       <c r="AP521" s="7"/>
     </row>
-    <row r="522" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A522" s="85">
         <v>46218</v>
       </c>
@@ -53010,7 +53010,7 @@
       </c>
       <c r="AP522" s="7"/>
     </row>
-    <row r="523" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A523" s="85">
         <v>46218</v>
       </c>
@@ -53102,7 +53102,7 @@
       </c>
       <c r="AP523" s="7"/>
     </row>
-    <row r="524" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A524" s="85">
         <v>46218</v>
       </c>
@@ -53194,7 +53194,7 @@
       </c>
       <c r="AP524" s="7"/>
     </row>
-    <row r="525" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A525" s="85">
         <v>46218</v>
       </c>
@@ -53284,7 +53284,7 @@
       </c>
       <c r="AP525" s="7"/>
     </row>
-    <row r="526" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A526" s="85">
         <v>46218</v>
       </c>
@@ -53378,7 +53378,7 @@
       </c>
       <c r="AP526" s="7"/>
     </row>
-    <row r="527" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A527" s="85">
         <v>46218</v>
       </c>
@@ -53468,7 +53468,7 @@
       </c>
       <c r="AP527" s="7"/>
     </row>
-    <row r="528" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A528" s="85">
         <v>46218</v>
       </c>
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AP528" s="7"/>
     </row>
-    <row r="529" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A529" s="85">
         <v>46218</v>
       </c>
@@ -53648,7 +53648,7 @@
       </c>
       <c r="AP529" s="7"/>
     </row>
-    <row r="530" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A530" s="85">
         <v>46218</v>
       </c>
@@ -53738,7 +53738,7 @@
       </c>
       <c r="AP530" s="7"/>
     </row>
-    <row r="531" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A531" s="85">
         <v>46218</v>
       </c>
@@ -53830,7 +53830,7 @@
       </c>
       <c r="AP531" s="7"/>
     </row>
-    <row r="532" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="85">
         <v>46218</v>
       </c>
@@ -54943,7 +54943,7 @@
       </c>
       <c r="AP543" s="7"/>
     </row>
-    <row r="544" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A544" s="85">
         <v>46219</v>
       </c>
@@ -55033,7 +55033,7 @@
       </c>
       <c r="AP544" s="7"/>
     </row>
-    <row r="545" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A545" s="85">
         <v>46219</v>
       </c>
@@ -55125,7 +55125,7 @@
       </c>
       <c r="AP545" s="7"/>
     </row>
-    <row r="546" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A546" s="85">
         <v>46219</v>
       </c>
@@ -55215,7 +55215,7 @@
       </c>
       <c r="AP546" s="7"/>
     </row>
-    <row r="547" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A547" s="85">
         <v>46219</v>
       </c>
@@ -55305,7 +55305,7 @@
       </c>
       <c r="AP547" s="7"/>
     </row>
-    <row r="548" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A548" s="85">
         <v>46219</v>
       </c>
@@ -55395,7 +55395,7 @@
       </c>
       <c r="AP548" s="7"/>
     </row>
-    <row r="549" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A549" s="85">
         <v>46219</v>
       </c>
@@ -55487,7 +55487,7 @@
       </c>
       <c r="AP549" s="7"/>
     </row>
-    <row r="550" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A550" s="85">
         <v>46219</v>
       </c>
@@ -55577,7 +55577,7 @@
       </c>
       <c r="AP550" s="7"/>
     </row>
-    <row r="551" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A551" s="85">
         <v>46219</v>
       </c>
@@ -55667,7 +55667,7 @@
       </c>
       <c r="AP551" s="7"/>
     </row>
-    <row r="552" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A552" s="85">
         <v>46219</v>
       </c>
@@ -55759,7 +55759,7 @@
       </c>
       <c r="AP552" s="7"/>
     </row>
-    <row r="553" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="85">
         <v>46220</v>
       </c>
@@ -55855,7 +55855,7 @@
       </c>
       <c r="AP553" s="7"/>
     </row>
-    <row r="554" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="85">
         <v>46220</v>
       </c>
@@ -55951,7 +55951,7 @@
       </c>
       <c r="AP554" s="7"/>
     </row>
-    <row r="555" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="85">
         <v>46220</v>
       </c>
@@ -56047,7 +56047,7 @@
       </c>
       <c r="AP555" s="7"/>
     </row>
-    <row r="556" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="85">
         <v>46220</v>
       </c>
@@ -56143,7 +56143,7 @@
       </c>
       <c r="AP556" s="7"/>
     </row>
-    <row r="557" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="85">
         <v>46220</v>
       </c>
@@ -57707,7 +57707,7 @@
       </c>
       <c r="AP573" s="7"/>
     </row>
-    <row r="574" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A574" s="85">
         <v>46220</v>
       </c>
@@ -57797,7 +57797,7 @@
       </c>
       <c r="AP574" s="7"/>
     </row>
-    <row r="575" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A575" s="85">
         <v>46220</v>
       </c>
@@ -57887,7 +57887,7 @@
       </c>
       <c r="AP575" s="7"/>
     </row>
-    <row r="576" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A576" s="85">
         <v>46220</v>
       </c>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="AP576" s="7"/>
     </row>
-    <row r="577" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A577" s="85">
         <v>46220</v>
       </c>
@@ -58076,7 +58076,7 @@
       </c>
       <c r="AP577" s="7"/>
     </row>
-    <row r="578" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A578" s="85">
         <v>46220</v>
       </c>
@@ -58178,7 +58178,7 @@
       </c>
       <c r="AP578" s="7"/>
     </row>
-    <row r="579" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A579" s="85">
         <v>46220</v>
       </c>
@@ -58272,7 +58272,7 @@
       </c>
       <c r="AP579" s="7"/>
     </row>
-    <row r="580" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A580" s="85">
         <v>46220</v>
       </c>
@@ -58370,7 +58370,7 @@
       </c>
       <c r="AP580" s="7"/>
     </row>
-    <row r="581" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A581" s="85">
         <v>46220</v>
       </c>
@@ -58468,7 +58468,7 @@
       </c>
       <c r="AP581" s="7"/>
     </row>
-    <row r="582" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A582" s="85">
         <v>46220</v>
       </c>
@@ -58558,7 +58558,7 @@
       </c>
       <c r="AP582" s="7"/>
     </row>
-    <row r="583" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A583" s="85">
         <v>46220</v>
       </c>
@@ -58648,7 +58648,7 @@
       </c>
       <c r="AP583" s="7"/>
     </row>
-    <row r="584" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A584" s="85">
         <v>46220</v>
       </c>
@@ -58738,7 +58738,7 @@
       </c>
       <c r="AP584" s="7"/>
     </row>
-    <row r="585" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A585" s="85">
         <v>46220</v>
       </c>
@@ -58828,7 +58828,7 @@
       </c>
       <c r="AP585" s="7"/>
     </row>
-    <row r="586" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A586" s="85">
         <v>46220</v>
       </c>
@@ -58918,7 +58918,7 @@
       </c>
       <c r="AP586" s="7"/>
     </row>
-    <row r="587" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A587" s="85">
         <v>46220</v>
       </c>
@@ -59008,7 +59008,7 @@
       </c>
       <c r="AP587" s="7"/>
     </row>
-    <row r="588" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A588" s="85">
         <v>46220</v>
       </c>
@@ -59070,7 +59070,7 @@
       <c r="AL588" s="112"/>
       <c r="AP588" s="7"/>
     </row>
-    <row r="589" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A589" s="85">
         <v>46220</v>
       </c>
@@ -59132,7 +59132,7 @@
       <c r="AL589" s="112"/>
       <c r="AP589" s="7"/>
     </row>
-    <row r="590" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A590" s="85">
         <v>46220</v>
       </c>
@@ -59194,7 +59194,7 @@
       <c r="AL590" s="112"/>
       <c r="AP590" s="7"/>
     </row>
-    <row r="591" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A591" s="85">
         <v>46220</v>
       </c>
@@ -59256,7 +59256,7 @@
       <c r="AL591" s="112"/>
       <c r="AP591" s="7"/>
     </row>
-    <row r="592" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A592" s="85">
         <v>46220</v>
       </c>
@@ -59326,7 +59326,7 @@
       <c r="AL592" s="112"/>
       <c r="AP592" s="7"/>
     </row>
-    <row r="593" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A593" s="85">
         <v>46220</v>
       </c>
@@ -59388,7 +59388,7 @@
       <c r="AL593" s="112"/>
       <c r="AP593" s="7"/>
     </row>
-    <row r="594" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="85">
         <v>46221</v>
       </c>
@@ -59456,7 +59456,7 @@
       <c r="AL594" s="112"/>
       <c r="AP594" s="7"/>
     </row>
-    <row r="595" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="85">
         <v>46221</v>
       </c>
@@ -59524,7 +59524,7 @@
       <c r="AL595" s="112"/>
       <c r="AP595" s="7"/>
     </row>
-    <row r="596" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="85">
         <v>46221</v>
       </c>
@@ -59590,7 +59590,7 @@
       <c r="AL596" s="112"/>
       <c r="AP596" s="7"/>
     </row>
-    <row r="597" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="85">
         <v>46221</v>
       </c>
@@ -59658,7 +59658,7 @@
       <c r="AL597" s="112"/>
       <c r="AP597" s="7"/>
     </row>
-    <row r="598" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="85">
         <v>46221</v>
       </c>
@@ -59726,7 +59726,7 @@
       <c r="AL598" s="112"/>
       <c r="AP598" s="7"/>
     </row>
-    <row r="599" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="85">
         <v>46221</v>
       </c>
@@ -59794,7 +59794,7 @@
       <c r="AL599" s="112"/>
       <c r="AP599" s="7"/>
     </row>
-    <row r="600" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="85">
         <v>46221</v>
       </c>
@@ -60446,7 +60446,7 @@
       <c r="AL609" s="112"/>
       <c r="AP609" s="7"/>
     </row>
-    <row r="610" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="85">
         <v>46221</v>
       </c>
@@ -60826,7 +60826,7 @@
       <c r="AL615" s="112"/>
       <c r="AP615" s="7"/>
     </row>
-    <row r="616" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A616" s="85">
         <v>46221</v>
       </c>
@@ -60896,7 +60896,7 @@
       <c r="AL616" s="112"/>
       <c r="AP616" s="7"/>
     </row>
-    <row r="617" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A617" s="85">
         <v>46221</v>
       </c>
@@ -60958,7 +60958,7 @@
       <c r="AL617" s="112"/>
       <c r="AP617" s="7"/>
     </row>
-    <row r="618" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A618" s="85">
         <v>46221</v>
       </c>
@@ -61020,7 +61020,7 @@
       <c r="AL618" s="112"/>
       <c r="AP618" s="7"/>
     </row>
-    <row r="619" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A619" s="85">
         <v>46221</v>
       </c>
@@ -61082,7 +61082,7 @@
       <c r="AL619" s="112"/>
       <c r="AP619" s="7"/>
     </row>
-    <row r="620" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A620" s="85">
         <v>46221</v>
       </c>
@@ -61144,7 +61144,7 @@
       <c r="AL620" s="112"/>
       <c r="AP620" s="7"/>
     </row>
-    <row r="621" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A621" s="85">
         <v>46221</v>
       </c>
@@ -61206,7 +61206,7 @@
       <c r="AL621" s="112"/>
       <c r="AP621" s="7"/>
     </row>
-    <row r="622" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A622" s="85">
         <v>46221</v>
       </c>
@@ -61268,7 +61268,7 @@
       <c r="AL622" s="112"/>
       <c r="AP622" s="7"/>
     </row>
-    <row r="623" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A623" s="85">
         <v>46221</v>
       </c>
@@ -61330,7 +61330,7 @@
       <c r="AL623" s="112"/>
       <c r="AP623" s="7"/>
     </row>
-    <row r="624" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A624" s="85">
         <v>46221</v>
       </c>
@@ -61392,7 +61392,7 @@
       <c r="AL624" s="112"/>
       <c r="AP624" s="7"/>
     </row>
-    <row r="625" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A625" s="85">
         <v>46221</v>
       </c>
@@ -61454,7 +61454,7 @@
       <c r="AL625" s="112"/>
       <c r="AP625" s="7"/>
     </row>
-    <row r="626" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A626" s="85">
         <v>46221</v>
       </c>
@@ -61516,7 +61516,7 @@
       <c r="AL626" s="112"/>
       <c r="AP626" s="7"/>
     </row>
-    <row r="627" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A627" s="85">
         <v>46221</v>
       </c>
@@ -61578,7 +61578,7 @@
       <c r="AL627" s="112"/>
       <c r="AP627" s="7"/>
     </row>
-    <row r="628" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A628" s="85">
         <v>46221</v>
       </c>
@@ -61640,7 +61640,7 @@
       <c r="AL628" s="112"/>
       <c r="AP628" s="7"/>
     </row>
-    <row r="629" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A629" s="85">
         <v>46221</v>
       </c>
@@ -61704,7 +61704,7 @@
       <c r="AL629" s="112"/>
       <c r="AP629" s="7"/>
     </row>
-    <row r="630" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="85">
         <v>46223</v>
       </c>
@@ -61774,7 +61774,7 @@
       <c r="AL630" s="112"/>
       <c r="AP630" s="7"/>
     </row>
-    <row r="631" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="85">
         <v>46223</v>
       </c>
@@ -62352,7 +62352,7 @@
       <c r="AL639" s="112"/>
       <c r="AP639" s="7"/>
     </row>
-    <row r="640" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A640" s="85">
         <v>46223</v>
       </c>
@@ -62414,7 +62414,7 @@
       <c r="AL640" s="112"/>
       <c r="AP640" s="7"/>
     </row>
-    <row r="641" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A641" s="85">
         <v>46223</v>
       </c>
@@ -62476,7 +62476,7 @@
       <c r="AL641" s="112"/>
       <c r="AP641" s="7"/>
     </row>
-    <row r="642" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A642" s="85">
         <v>46223</v>
       </c>
@@ -62540,7 +62540,7 @@
       <c r="AL642" s="112"/>
       <c r="AP642" s="7"/>
     </row>
-    <row r="643" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A643" s="85">
         <v>46223</v>
       </c>
@@ -62602,7 +62602,7 @@
       <c r="AL643" s="112"/>
       <c r="AP643" s="7"/>
     </row>
-    <row r="644" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A644" s="85">
         <v>46223</v>
       </c>
@@ -62644,7 +62644,7 @@
         <v>6</v>
       </c>
       <c r="R644" s="104">
-        <f t="shared" ref="R644:R855" si="152">SUM(O644:Q644)</f>
+        <f t="shared" ref="R644:R742" si="152">SUM(O644:Q644)</f>
         <v>6</v>
       </c>
       <c r="S644" s="86">
@@ -62664,7 +62664,7 @@
       <c r="AL644" s="112"/>
       <c r="AP644" s="7"/>
     </row>
-    <row r="645" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A645" s="85">
         <v>46223</v>
       </c>
@@ -62726,7 +62726,7 @@
       <c r="AL645" s="112"/>
       <c r="AP645" s="7"/>
     </row>
-    <row r="646" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A646" s="85">
         <v>46223</v>
       </c>
@@ -62788,7 +62788,7 @@
       <c r="AL646" s="112"/>
       <c r="AP646" s="7"/>
     </row>
-    <row r="647" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A647" s="85">
         <v>46223</v>
       </c>
@@ -62850,7 +62850,7 @@
       <c r="AL647" s="112"/>
       <c r="AP647" s="7"/>
     </row>
-    <row r="648" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A648" s="85">
         <v>46223</v>
       </c>
@@ -62912,7 +62912,7 @@
       <c r="AL648" s="112"/>
       <c r="AP648" s="7"/>
     </row>
-    <row r="649" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A649" s="85">
         <v>46223</v>
       </c>
@@ -62974,7 +62974,7 @@
       <c r="AL649" s="112"/>
       <c r="AP649" s="7"/>
     </row>
-    <row r="650" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A650" s="85">
         <v>46223</v>
       </c>
@@ -63044,7 +63044,7 @@
       <c r="AL650" s="112"/>
       <c r="AP650" s="7"/>
     </row>
-    <row r="651" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A651" s="85">
         <v>46223</v>
       </c>
@@ -63106,7 +63106,7 @@
       <c r="AL651" s="112"/>
       <c r="AP651" s="7"/>
     </row>
-    <row r="652" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A652" s="85">
         <v>46223</v>
       </c>
@@ -63168,7 +63168,7 @@
       <c r="AL652" s="112"/>
       <c r="AP652" s="7"/>
     </row>
-    <row r="653" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A653" s="85">
         <v>46223</v>
       </c>
@@ -63230,7 +63230,7 @@
       <c r="AL653" s="112"/>
       <c r="AP653" s="7"/>
     </row>
-    <row r="654" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A654" s="85">
         <v>46223</v>
       </c>
@@ -63292,7 +63292,7 @@
       <c r="AL654" s="112"/>
       <c r="AP654" s="7"/>
     </row>
-    <row r="655" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A655" s="85">
         <v>46223</v>
       </c>
@@ -63364,7 +63364,7 @@
       <c r="AL655" s="112"/>
       <c r="AP655" s="7"/>
     </row>
-    <row r="656" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="85">
         <v>46224</v>
       </c>
@@ -63434,7 +63434,7 @@
       <c r="AL656" s="112"/>
       <c r="AP656" s="7"/>
     </row>
-    <row r="657" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="85">
         <v>46224</v>
       </c>
@@ -63504,7 +63504,7 @@
       <c r="AL657" s="112"/>
       <c r="AP657" s="7"/>
     </row>
-    <row r="658" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="85">
         <v>46224</v>
       </c>
@@ -63574,7 +63574,7 @@
       <c r="AL658" s="112"/>
       <c r="AP658" s="7"/>
     </row>
-    <row r="659" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="85">
         <v>46224</v>
       </c>
@@ -63644,7 +63644,7 @@
       <c r="AL659" s="112"/>
       <c r="AP659" s="7"/>
     </row>
-    <row r="660" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="85">
         <v>46224</v>
       </c>
@@ -64757,7 +64757,7 @@
       <c r="AL676" s="112"/>
       <c r="AP676" s="7"/>
     </row>
-    <row r="677" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A677" s="85">
         <v>46224</v>
       </c>
@@ -64825,7 +64825,7 @@
       <c r="AL677" s="112"/>
       <c r="AP677" s="7"/>
     </row>
-    <row r="678" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A678" s="85">
         <v>46224</v>
       </c>
@@ -64887,7 +64887,7 @@
       <c r="AL678" s="112"/>
       <c r="AP678" s="7"/>
     </row>
-    <row r="679" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A679" s="85">
         <v>46224</v>
       </c>
@@ -64949,7 +64949,7 @@
       <c r="AL679" s="112"/>
       <c r="AP679" s="7"/>
     </row>
-    <row r="680" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A680" s="85">
         <v>46224</v>
       </c>
@@ -65011,7 +65011,7 @@
       <c r="AL680" s="112"/>
       <c r="AP680" s="7"/>
     </row>
-    <row r="681" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A681" s="85">
         <v>46224</v>
       </c>
@@ -65073,7 +65073,7 @@
       <c r="AL681" s="112"/>
       <c r="AP681" s="7"/>
     </row>
-    <row r="682" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A682" s="85">
         <v>46224</v>
       </c>
@@ -65135,7 +65135,7 @@
       <c r="AL682" s="112"/>
       <c r="AP682" s="7"/>
     </row>
-    <row r="683" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A683" s="85">
         <v>46224</v>
       </c>
@@ -65197,7 +65197,7 @@
       <c r="AL683" s="112"/>
       <c r="AP683" s="7"/>
     </row>
-    <row r="684" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A684" s="85">
         <v>46224</v>
       </c>
@@ -65259,7 +65259,7 @@
       <c r="AL684" s="112"/>
       <c r="AP684" s="7"/>
     </row>
-    <row r="685" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A685" s="85">
         <v>46224</v>
       </c>
@@ -65321,7 +65321,7 @@
       <c r="AL685" s="112"/>
       <c r="AP685" s="7"/>
     </row>
-    <row r="686" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A686" s="85">
         <v>46224</v>
       </c>
@@ -65833,7 +65833,7 @@
       <c r="AL693" s="112"/>
       <c r="AP693" s="7"/>
     </row>
-    <row r="694" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A694" s="85">
         <v>46225</v>
       </c>
@@ -65899,7 +65899,7 @@
       <c r="AL694" s="112"/>
       <c r="AP694" s="7"/>
     </row>
-    <row r="695" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A695" s="85">
         <v>46225</v>
       </c>
@@ -65961,7 +65961,7 @@
       <c r="AL695" s="112"/>
       <c r="AP695" s="7"/>
     </row>
-    <row r="696" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A696" s="85">
         <v>46225</v>
       </c>
@@ -66023,7 +66023,7 @@
       <c r="AL696" s="112"/>
       <c r="AP696" s="7"/>
     </row>
-    <row r="697" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A697" s="85">
         <v>46225</v>
       </c>
@@ -66085,7 +66085,7 @@
       <c r="AL697" s="112"/>
       <c r="AP697" s="7"/>
     </row>
-    <row r="698" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A698" s="85">
         <v>46225</v>
       </c>
@@ -66147,7 +66147,7 @@
       <c r="AL698" s="112"/>
       <c r="AP698" s="7"/>
     </row>
-    <row r="699" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A699" s="85">
         <v>46225</v>
       </c>
@@ -66213,7 +66213,7 @@
       <c r="AL699" s="112"/>
       <c r="AP699" s="7"/>
     </row>
-    <row r="700" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A700" s="85">
         <v>46225</v>
       </c>
@@ -66275,7 +66275,7 @@
       <c r="AL700" s="112"/>
       <c r="AP700" s="7"/>
     </row>
-    <row r="701" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A701" s="85">
         <v>46225</v>
       </c>
@@ -66337,7 +66337,7 @@
       <c r="AL701" s="112"/>
       <c r="AP701" s="7"/>
     </row>
-    <row r="702" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A702" s="85">
         <v>46225</v>
       </c>
@@ -66399,7 +66399,7 @@
       <c r="AL702" s="112"/>
       <c r="AP702" s="7"/>
     </row>
-    <row r="703" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A703" s="85">
         <v>46225</v>
       </c>
@@ -66465,7 +66465,7 @@
       <c r="AL703" s="112"/>
       <c r="AP703" s="7"/>
     </row>
-    <row r="704" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A704" s="85">
         <v>46225</v>
       </c>
@@ -66527,7 +66527,7 @@
       <c r="AL704" s="112"/>
       <c r="AP704" s="7"/>
     </row>
-    <row r="705" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A705" s="85">
         <v>46225</v>
       </c>
@@ -66589,7 +66589,7 @@
       <c r="AL705" s="112"/>
       <c r="AP705" s="7"/>
     </row>
-    <row r="706" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A706" s="85">
         <v>46225</v>
       </c>
@@ -66651,7 +66651,7 @@
       <c r="AL706" s="112"/>
       <c r="AP706" s="7"/>
     </row>
-    <row r="707" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A707" s="85">
         <v>46225</v>
       </c>
@@ -66713,7 +66713,7 @@
       <c r="AL707" s="112"/>
       <c r="AP707" s="7"/>
     </row>
-    <row r="708" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A708" s="85">
         <v>46225</v>
       </c>
@@ -66775,7 +66775,7 @@
       <c r="AL708" s="112"/>
       <c r="AP708" s="7"/>
     </row>
-    <row r="709" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A709" s="85">
         <v>46225</v>
       </c>
@@ -66839,7 +66839,7 @@
       <c r="AL709" s="112"/>
       <c r="AP709" s="7"/>
     </row>
-    <row r="710" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A710" s="85">
         <v>46225</v>
       </c>
@@ -66903,7 +66903,7 @@
       <c r="AL710" s="112"/>
       <c r="AP710" s="7"/>
     </row>
-    <row r="711" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="85">
         <v>46226</v>
       </c>
@@ -66973,7 +66973,7 @@
       <c r="AL711" s="112"/>
       <c r="AP711" s="7"/>
     </row>
-    <row r="712" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="85">
         <v>46226</v>
       </c>
@@ -67035,7 +67035,7 @@
       <c r="AL712" s="112"/>
       <c r="AP712" s="7"/>
     </row>
-    <row r="713" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="85">
         <v>46226</v>
       </c>
@@ -67105,7 +67105,7 @@
       <c r="AL713" s="112"/>
       <c r="AP713" s="7"/>
     </row>
-    <row r="714" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="85">
         <v>46226</v>
       </c>
@@ -67175,7 +67175,7 @@
       <c r="AL714" s="112"/>
       <c r="AP714" s="7"/>
     </row>
-    <row r="715" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A715" s="85">
         <v>46226</v>
       </c>
@@ -67243,7 +67243,7 @@
       <c r="AL715" s="112"/>
       <c r="AP715" s="7"/>
     </row>
-    <row r="716" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A716" s="85">
         <v>46226</v>
       </c>
@@ -67311,7 +67311,7 @@
       <c r="AL716" s="112"/>
       <c r="AP716" s="7"/>
     </row>
-    <row r="717" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717" s="85">
         <v>46226</v>
       </c>
@@ -67381,7 +67381,7 @@
       <c r="AL717" s="112"/>
       <c r="AP717" s="7"/>
     </row>
-    <row r="718" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A718" s="85">
         <v>46226</v>
       </c>
@@ -67447,7 +67447,7 @@
       <c r="AL718" s="112"/>
       <c r="AP718" s="7"/>
     </row>
-    <row r="719" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A719" s="85">
         <v>46226</v>
       </c>
@@ -68525,7 +68525,7 @@
       <c r="AL734" s="112"/>
       <c r="AP734" s="7"/>
     </row>
-    <row r="735" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A735" s="85">
         <v>46227</v>
       </c>
@@ -68733,7 +68733,7 @@
       <c r="AL737" s="112"/>
       <c r="AP737" s="7"/>
     </row>
-    <row r="738" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738" s="85">
         <v>46228</v>
       </c>
@@ -68805,7 +68805,7 @@
       <c r="AL738" s="112"/>
       <c r="AP738" s="7"/>
     </row>
-    <row r="739" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739" s="85">
         <v>46228</v>
       </c>
@@ -68871,7 +68871,7 @@
       <c r="AL739" s="112"/>
       <c r="AP739" s="7"/>
     </row>
-    <row r="740" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740" s="85">
         <v>46228</v>
       </c>
@@ -68933,7 +68933,7 @@
       <c r="AL740" s="112"/>
       <c r="AP740" s="7"/>
     </row>
-    <row r="741" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741" s="85">
         <v>46230</v>
       </c>
@@ -68997,7 +68997,7 @@
       <c r="AL741" s="112"/>
       <c r="AP741" s="7"/>
     </row>
-    <row r="742" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742" s="85">
         <v>46230</v>
       </c>
@@ -69067,7 +69067,7 @@
       <c r="AL742" s="112"/>
       <c r="AP742" s="7"/>
     </row>
-    <row r="743" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A743" s="85">
         <v>46230</v>
       </c>
@@ -69937,7 +69937,7 @@
       <c r="AL755" s="112"/>
       <c r="AP755" s="7"/>
     </row>
-    <row r="756" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A756" s="85">
         <v>46230</v>
       </c>
@@ -69999,7 +69999,7 @@
       <c r="AL756" s="112"/>
       <c r="AP756" s="7"/>
     </row>
-    <row r="757" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A757" s="85">
         <v>46230</v>
       </c>
@@ -70061,7 +70061,7 @@
       <c r="AL757" s="112"/>
       <c r="AP757" s="7"/>
     </row>
-    <row r="758" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A758" s="85">
         <v>46230</v>
       </c>
@@ -70129,7 +70129,7 @@
       <c r="AL758" s="112"/>
       <c r="AP758" s="7"/>
     </row>
-    <row r="759" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A759" s="85">
         <v>46230</v>
       </c>
@@ -70201,7 +70201,7 @@
       <c r="AL759" s="112"/>
       <c r="AP759" s="7"/>
     </row>
-    <row r="760" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A760" s="85">
         <v>46230</v>
       </c>
@@ -70273,7 +70273,7 @@
       <c r="AL760" s="112"/>
       <c r="AP760" s="7"/>
     </row>
-    <row r="761" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A761" s="85">
         <v>46230</v>
       </c>
@@ -70335,7 +70335,7 @@
       <c r="AL761" s="112"/>
       <c r="AP761" s="7"/>
     </row>
-    <row r="762" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A762" s="85">
         <v>46230</v>
       </c>
@@ -70397,7 +70397,7 @@
       <c r="AL762" s="112"/>
       <c r="AP762" s="7"/>
     </row>
-    <row r="763" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A763" s="85">
         <v>46230</v>
       </c>
@@ -70463,7 +70463,7 @@
       <c r="AL763" s="112"/>
       <c r="AP763" s="7"/>
     </row>
-    <row r="764" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A764" s="85">
         <v>46231</v>
       </c>
@@ -70533,7 +70533,7 @@
       <c r="AL764" s="112"/>
       <c r="AP764" s="7"/>
     </row>
-    <row r="765" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A765" s="85">
         <v>46231</v>
       </c>
@@ -70601,7 +70601,7 @@
       <c r="AL765" s="112"/>
       <c r="AP765" s="7"/>
     </row>
-    <row r="766" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A766" s="85">
         <v>46231</v>
       </c>
@@ -70669,7 +70669,7 @@
       <c r="AL766" s="112"/>
       <c r="AP766" s="7"/>
     </row>
-    <row r="767" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A767" s="85">
         <v>46231</v>
       </c>
@@ -71279,7 +71279,7 @@
       <c r="AL775" s="112"/>
       <c r="AP775" s="7"/>
     </row>
-    <row r="776" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A776" s="85">
         <v>46231</v>
       </c>
@@ -71347,7 +71347,7 @@
       <c r="AL776" s="112"/>
       <c r="AP776" s="7"/>
     </row>
-    <row r="777" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A777" s="85">
         <v>46231</v>
       </c>
@@ -71393,11 +71393,11 @@
         <v>15</v>
       </c>
       <c r="R777" s="104">
-        <f t="shared" ref="R777:R795" si="160">SUM(O777:Q777)</f>
+        <f t="shared" ref="R777:R794" si="160">SUM(O777:Q777)</f>
         <v>40</v>
       </c>
       <c r="S777" s="86">
-        <f t="shared" ref="S777:S795" si="161">R777+N777+J777</f>
+        <f t="shared" ref="S777:S794" si="161">R777+N777+J777</f>
         <v>40</v>
       </c>
       <c r="AB777" s="111"/>
@@ -71413,7 +71413,7 @@
       <c r="AL777" s="112"/>
       <c r="AP777" s="7"/>
     </row>
-    <row r="778" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A778" s="85">
         <v>46231</v>
       </c>
@@ -71485,7 +71485,7 @@
       <c r="AL778" s="112"/>
       <c r="AP778" s="7"/>
     </row>
-    <row r="779" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A779" s="85">
         <v>46231</v>
       </c>
@@ -71547,7 +71547,7 @@
       <c r="AL779" s="112"/>
       <c r="AP779" s="7"/>
     </row>
-    <row r="780" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A780" s="85">
         <v>46231</v>
       </c>
@@ -71609,7 +71609,7 @@
       <c r="AL780" s="112"/>
       <c r="AP780" s="7"/>
     </row>
-    <row r="781" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A781" s="85">
         <v>46231</v>
       </c>
@@ -72573,11 +72573,11 @@
         <v>6</v>
       </c>
       <c r="R795" s="104">
-        <f t="shared" ref="R795:R823" si="162">SUM(O795:Q795)</f>
+        <f t="shared" ref="R795:R821" si="162">SUM(O795:Q795)</f>
         <v>6</v>
       </c>
       <c r="S795" s="86">
-        <f t="shared" ref="S795:S823" si="163">R795+N795+J795</f>
+        <f t="shared" ref="S795:S821" si="163">R795+N795+J795</f>
         <v>6</v>
       </c>
       <c r="AB795" s="111"/>
@@ -73041,7 +73041,7 @@
       <c r="AL802" s="112"/>
       <c r="AP802" s="7"/>
     </row>
-    <row r="803" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A803" s="85">
         <v>46232</v>
       </c>
@@ -74201,7 +74201,7 @@
       <c r="AL820" s="112"/>
       <c r="AP820" s="7"/>
     </row>
-    <row r="821" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A821" s="85">
         <v>46233</v>
       </c>
@@ -74269,7 +74269,7 @@
       <c r="AL821" s="112"/>
       <c r="AP821" s="7"/>
     </row>
-    <row r="822" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A822" s="85">
         <v>46233</v>
       </c>
@@ -74311,11 +74311,11 @@
       <c r="P822" s="52"/>
       <c r="Q822" s="52"/>
       <c r="R822" s="104">
-        <f t="shared" ref="R822:R834" si="165">SUM(O822:Q822)</f>
+        <f t="shared" ref="R822:R832" si="165">SUM(O822:Q822)</f>
         <v>0</v>
       </c>
       <c r="S822" s="86">
-        <f t="shared" ref="S822:S834" si="166">R822+N822+J822</f>
+        <f t="shared" ref="S822:S832" si="166">R822+N822+J822</f>
         <v>10</v>
       </c>
       <c r="AB822" s="111"/>
@@ -74331,7 +74331,7 @@
       <c r="AL822" s="112"/>
       <c r="AP822" s="7"/>
     </row>
-    <row r="823" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A823" s="85">
         <v>46233</v>
       </c>
@@ -74393,7 +74393,7 @@
       <c r="AL823" s="112"/>
       <c r="AP823" s="7"/>
     </row>
-    <row r="824" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A824" s="85">
         <v>46233</v>
       </c>
@@ -74455,7 +74455,7 @@
       <c r="AL824" s="112"/>
       <c r="AP824" s="7"/>
     </row>
-    <row r="825" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A825" s="85">
         <v>46233</v>
       </c>
@@ -74517,7 +74517,7 @@
       <c r="AL825" s="112"/>
       <c r="AP825" s="7"/>
     </row>
-    <row r="826" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A826" s="85">
         <v>46233</v>
       </c>
@@ -74581,7 +74581,7 @@
       <c r="AL826" s="112"/>
       <c r="AP826" s="7"/>
     </row>
-    <row r="827" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A827" s="85">
         <v>46233</v>
       </c>
@@ -74647,7 +74647,7 @@
       <c r="AL827" s="112"/>
       <c r="AP827" s="7"/>
     </row>
-    <row r="828" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A828" s="85">
         <v>46233</v>
       </c>
@@ -74713,7 +74713,7 @@
       <c r="AL828" s="112"/>
       <c r="AP828" s="7"/>
     </row>
-    <row r="829" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A829" s="85">
         <v>46233</v>
       </c>
@@ -74785,7 +74785,7 @@
       <c r="AL829" s="112"/>
       <c r="AP829" s="7"/>
     </row>
-    <row r="830" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A830" s="85">
         <v>46233</v>
       </c>
@@ -74857,7 +74857,7 @@
       <c r="AL830" s="112"/>
       <c r="AP830" s="7"/>
     </row>
-    <row r="831" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A831" s="85">
         <v>46234</v>
       </c>
@@ -75000,7 +75000,7 @@
       <c r="AL832" s="112"/>
       <c r="AP832" s="7"/>
     </row>
-    <row r="833" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A833" s="85">
         <v>46234</v>
       </c>
@@ -75072,7 +75072,7 @@
       <c r="AL833" s="112"/>
       <c r="AP833" s="7"/>
     </row>
-    <row r="834" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A834" s="85">
         <v>46234</v>
       </c>
@@ -75140,7 +75140,7 @@
       <c r="AL834" s="112"/>
       <c r="AP834" s="7"/>
     </row>
-    <row r="835" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A835" s="85">
         <v>46234</v>
       </c>
@@ -75210,7 +75210,7 @@
       <c r="AL835" s="112"/>
       <c r="AP835" s="7"/>
     </row>
-    <row r="836" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A836" s="85">
         <v>46234</v>
       </c>
@@ -75282,7 +75282,7 @@
       <c r="AL836" s="112"/>
       <c r="AP836" s="7"/>
     </row>
-    <row r="837" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A837" s="85">
         <v>46234</v>
       </c>
@@ -75352,7 +75352,7 @@
       <c r="AL837" s="112"/>
       <c r="AP837" s="7"/>
     </row>
-    <row r="838" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A838" s="85">
         <v>46234</v>
       </c>
@@ -75416,7 +75416,7 @@
       <c r="AL838" s="112"/>
       <c r="AP838" s="7"/>
     </row>
-    <row r="839" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A839" s="85">
         <v>46234</v>
       </c>
@@ -75488,7 +75488,7 @@
       <c r="AL839" s="112"/>
       <c r="AP839" s="7"/>
     </row>
-    <row r="840" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A840" s="85">
         <v>46234</v>
       </c>
@@ -75554,7 +75554,7 @@
       <c r="AL840" s="112"/>
       <c r="AP840" s="7"/>
     </row>
-    <row r="841" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A841" s="85">
         <v>46234</v>
       </c>
@@ -76014,7 +76014,7 @@
       <c r="AL847" s="112"/>
       <c r="AP847" s="7"/>
     </row>
-    <row r="848" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A848" s="85">
         <v>46234</v>
       </c>
@@ -76125,7 +76125,7 @@
       <c r="AL849" s="112"/>
       <c r="AP849" s="7"/>
     </row>
-    <row r="850" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A850" s="85">
         <v>46234</v>
       </c>
@@ -76530,7 +76530,7 @@
       <c r="L858" s="52"/>
       <c r="M858" s="52"/>
       <c r="N858" s="104">
-        <f t="shared" ref="N857:N860" si="173">K858+L858+M858</f>
+        <f t="shared" ref="N858:N860" si="173">K858+L858+M858</f>
         <v>0</v>
       </c>
       <c r="O858" s="52"/>
@@ -76607,11 +76607,11 @@
       <c r="P859" s="52"/>
       <c r="Q859" s="52"/>
       <c r="R859" s="104">
-        <f t="shared" ref="R857:R860" si="174">SUM(O859:Q859)</f>
+        <f t="shared" ref="R859:R860" si="174">SUM(O859:Q859)</f>
         <v>0</v>
       </c>
       <c r="S859" s="86">
-        <f t="shared" ref="S857:S860" si="175">R859+N859+J859</f>
+        <f t="shared" ref="S859:S860" si="175">R859+N859+J859</f>
         <v>0</v>
       </c>
       <c r="AB859" s="88">
@@ -76904,9 +76904,9 @@
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="5">
+    <filterColumn colId="7">
       <filters>
-        <filter val="LMT"/>
+        <filter val="Zeshan"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10" showButton="0"/>
@@ -76923,13 +76923,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -76942,14 +76943,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
